--- a/output/donnée_vente_E-commerce_13-03-2026_03-25.xlsx
+++ b/output/donnée_vente_E-commerce_13-03-2026_03-25.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahmoud At-Tidianie\Desktop\GITHUB\Exo-de-donn-e-E-commerce-\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView minimized="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Données Brutes" sheetId="1" r:id="rId1"/>
     <sheet name="Données Néttoyées" sheetId="2" r:id="rId2"/>
     <sheet name="Données Par Catégories" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -435,11 +440,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,11 +508,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -549,7 +562,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -581,9 +594,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -615,6 +629,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -790,9 +805,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
@@ -809,7 +824,7 @@
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -850,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -891,7 +906,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -932,7 +947,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -973,7 +988,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1014,7 +1029,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1055,7 +1070,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1093,7 +1108,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1134,7 +1149,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1175,7 +1190,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1216,7 +1231,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1257,9 +1272,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
@@ -1279,7 +1294,7 @@
     <col min="16" max="16" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1329,7 +1344,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1379,7 +1394,7 @@
         <v>899.99</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1429,7 +1444,7 @@
         <v>1799.98</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1479,7 +1494,7 @@
         <v>427.49</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1529,7 +1544,7 @@
         <v>509.97</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1579,7 +1594,7 @@
         <v>1299.99</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1629,7 +1644,7 @@
         <v>959.98</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1679,7 +1694,7 @@
         <v>629.99</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1729,7 +1744,7 @@
         <v>854.99</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1779,7 +1794,7 @@
         <v>549.99</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1835,16 +1850,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
     <col min="3" max="3" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1855,7 +1870,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>199.99</v>
       </c>
@@ -1866,7 +1881,7 @@
         <v>599.97</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>549.99</v>
       </c>
@@ -1877,7 +1892,7 @@
         <v>949.98</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>899.99</v>
       </c>
@@ -1888,7 +1903,7 @@
         <v>899.99</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1299.99</v>
       </c>
@@ -1899,7 +1914,7 @@
         <v>2199.98</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>999.99</v>
       </c>
@@ -1910,7 +1925,7 @@
         <v>2699.97</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>449.99</v>
       </c>
